--- a/filer/26259495_coop_danmark_a_s.xlsx
+++ b/filer/26259495_coop_danmark_a_s.xlsx
@@ -7937,7 +7937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8371,21 +8371,19 @@
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>fsa:IncomeFromSecuritiesAsNoncurrentAssets</t>
+          <t>fsa:InvestmentsGross</t>
         </is>
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>fsa:IncomeFromSecuritiesAsNoncurrentAssets</t>
+          <t>fsa:InvestmentsGross</t>
         </is>
       </c>
       <c r="D15" s="35" t="n"/>
       <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n">
-        <v>49000</v>
-      </c>
+      <c r="F15" s="35" t="n"/>
       <c r="G15" s="35" t="n">
-        <v>43000</v>
+        <v>429000</v>
       </c>
       <c r="H15" s="35" t="n"/>
       <c r="I15" s="36" t="inlineStr">
@@ -8402,21 +8400,29 @@
       </c>
       <c r="B16" s="37" t="inlineStr">
         <is>
-          <t>fsa:InvestmentsGross</t>
+          <t>fsa:LongtermDeferredIncome</t>
         </is>
       </c>
       <c r="C16" s="37" t="inlineStr">
         <is>
-          <t>fsa:InvestmentsGross</t>
-        </is>
-      </c>
-      <c r="D16" s="38" t="n"/>
-      <c r="E16" s="38" t="n"/>
-      <c r="F16" s="38" t="n"/>
+          <t>fsa:LongtermDeferredIncome</t>
+        </is>
+      </c>
+      <c r="D16" s="38" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E16" s="38" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F16" s="38" t="n">
+        <v>55000</v>
+      </c>
       <c r="G16" s="38" t="n">
-        <v>429000</v>
-      </c>
-      <c r="H16" s="38" t="n"/>
+        <v>57000</v>
+      </c>
+      <c r="H16" s="38" t="n">
+        <v>49000</v>
+      </c>
       <c r="I16" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8431,28 +8437,20 @@
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>fsa:LongtermDeferredIncome</t>
+          <t>fsa:LongtermParticipatingInterests</t>
         </is>
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>fsa:LongtermDeferredIncome</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E17" s="35" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F17" s="35" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G17" s="35" t="n">
-        <v>57000</v>
-      </c>
+          <t>fsa:LongtermParticipatingInterests</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="35" t="n"/>
       <c r="H17" s="35" t="n">
-        <v>49000</v>
+        <v>15000</v>
       </c>
       <c r="I17" s="36" t="inlineStr">
         <is>
@@ -8468,21 +8466,21 @@
       </c>
       <c r="B18" s="37" t="inlineStr">
         <is>
-          <t>fsa:LongtermParticipatingInterests</t>
+          <t>fsa:OtherAdjustmentsRelatedToInvestments</t>
         </is>
       </c>
       <c r="C18" s="37" t="inlineStr">
         <is>
-          <t>fsa:LongtermParticipatingInterests</t>
+          <t>fsa:OtherAdjustmentsRelatedToInvestments</t>
         </is>
       </c>
       <c r="D18" s="38" t="n"/>
       <c r="E18" s="38" t="n"/>
       <c r="F18" s="38" t="n"/>
-      <c r="G18" s="38" t="n"/>
-      <c r="H18" s="38" t="n">
-        <v>15000</v>
-      </c>
+      <c r="G18" s="38" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="H18" s="38" t="n"/>
       <c r="I18" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8497,21 +8495,21 @@
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>fsa:OtherAdjustmentsRelatedToInvestments</t>
+          <t>fsa:OtherComponentsOfCashFlowsFromUsedInFinancingActivities</t>
         </is>
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>fsa:OtherAdjustmentsRelatedToInvestments</t>
+          <t>fsa:OtherComponentsOfCashFlowsFromUsedInFinancingActivities</t>
         </is>
       </c>
       <c r="D19" s="35" t="n"/>
       <c r="E19" s="35" t="n"/>
       <c r="F19" s="35" t="n"/>
-      <c r="G19" s="35" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="H19" s="35" t="n"/>
+      <c r="G19" s="35" t="n"/>
+      <c r="H19" s="35" t="n">
+        <v>213000</v>
+      </c>
       <c r="I19" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8526,21 +8524,21 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>fsa:OtherComponentsOfCashFlowsFromUsedInFinancingActivities</t>
+          <t>fsa:RaisingOfDebtToAssociates</t>
         </is>
       </c>
       <c r="C20" s="37" t="inlineStr">
         <is>
-          <t>fsa:OtherComponentsOfCashFlowsFromUsedInFinancingActivities</t>
-        </is>
-      </c>
-      <c r="D20" s="38" t="n"/>
+          <t>fsa:RaisingOfDebtToAssociates</t>
+        </is>
+      </c>
+      <c r="D20" s="38" t="n">
+        <v>6000</v>
+      </c>
       <c r="E20" s="38" t="n"/>
       <c r="F20" s="38" t="n"/>
       <c r="G20" s="38" t="n"/>
-      <c r="H20" s="38" t="n">
-        <v>213000</v>
-      </c>
+      <c r="H20" s="38" t="n"/>
       <c r="I20" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8555,20 +8553,20 @@
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>fsa:ProfitLossRelatedToInvestments</t>
+          <t>fsa:RepaymentOfMortgageDebt</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>fsa:ProfitLossRelatedToInvestments</t>
+          <t>fsa:RepaymentOfMortgageDebt</t>
         </is>
       </c>
       <c r="D21" s="35" t="n"/>
-      <c r="E21" s="35" t="n"/>
+      <c r="E21" s="35" t="n">
+        <v>127000</v>
+      </c>
       <c r="F21" s="35" t="n"/>
-      <c r="G21" s="35" t="n">
-        <v>-1000</v>
-      </c>
+      <c r="G21" s="35" t="n"/>
       <c r="H21" s="35" t="n"/>
       <c r="I21" s="36" t="inlineStr">
         <is>
@@ -8584,20 +8582,20 @@
       </c>
       <c r="B22" s="37" t="inlineStr">
         <is>
-          <t>fsa:RaisingOfDebtToAssociates</t>
+          <t>fsa:ReversalsOfImpairmentLossesOfIntangibleAssetsFromPreviousPeriods</t>
         </is>
       </c>
       <c r="C22" s="37" t="inlineStr">
         <is>
-          <t>fsa:RaisingOfDebtToAssociates</t>
-        </is>
-      </c>
-      <c r="D22" s="38" t="n">
-        <v>6000</v>
-      </c>
+          <t>fsa:ReversalsOfImpairmentLossesOfIntangibleAssetsFromPreviousPeriods</t>
+        </is>
+      </c>
+      <c r="D22" s="38" t="n"/>
       <c r="E22" s="38" t="n"/>
       <c r="F22" s="38" t="n"/>
-      <c r="G22" s="38" t="n"/>
+      <c r="G22" s="38" t="n">
+        <v>484000</v>
+      </c>
       <c r="H22" s="38" t="n"/>
       <c r="I22" s="39" t="inlineStr">
         <is>
@@ -8613,20 +8611,20 @@
       </c>
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>fsa:RepaymentOfMortgageDebt</t>
+          <t>fsa:ReversalsOfImpairmentLossesOfPropertyPlantAndEquipmentFromPreviousPeriods</t>
         </is>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
-          <t>fsa:RepaymentOfMortgageDebt</t>
+          <t>fsa:ReversalsOfImpairmentLossesOfPropertyPlantAndEquipmentFromPreviousPeriods</t>
         </is>
       </c>
       <c r="D23" s="35" t="n"/>
-      <c r="E23" s="35" t="n">
-        <v>127000</v>
-      </c>
+      <c r="E23" s="35" t="n"/>
       <c r="F23" s="35" t="n"/>
-      <c r="G23" s="35" t="n"/>
+      <c r="G23" s="35" t="n">
+        <v>149000</v>
+      </c>
       <c r="H23" s="35" t="n"/>
       <c r="I23" s="36" t="inlineStr">
         <is>
@@ -8642,21 +8640,21 @@
       </c>
       <c r="B24" s="37" t="inlineStr">
         <is>
-          <t>fsa:ReversalsOfImpairmentLossesOfIntangibleAssetsFromPreviousPeriods</t>
+          <t>fsa:SaleOfMinorityShares</t>
         </is>
       </c>
       <c r="C24" s="37" t="inlineStr">
         <is>
-          <t>fsa:ReversalsOfImpairmentLossesOfIntangibleAssetsFromPreviousPeriods</t>
+          <t>fsa:SaleOfMinorityShares</t>
         </is>
       </c>
       <c r="D24" s="38" t="n"/>
       <c r="E24" s="38" t="n"/>
       <c r="F24" s="38" t="n"/>
-      <c r="G24" s="38" t="n">
-        <v>484000</v>
-      </c>
-      <c r="H24" s="38" t="n"/>
+      <c r="G24" s="38" t="n"/>
+      <c r="H24" s="38" t="n">
+        <v>-5000</v>
+      </c>
       <c r="I24" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8671,19 +8669,25 @@
       </c>
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>fsa:ReversalsOfImpairmentLossesOfPropertyPlantAndEquipmentFromPreviousPeriods</t>
+          <t>fsa:ShorttermPayablesToAssociates</t>
         </is>
       </c>
       <c r="C25" s="34" t="inlineStr">
         <is>
-          <t>fsa:ReversalsOfImpairmentLossesOfPropertyPlantAndEquipmentFromPreviousPeriods</t>
-        </is>
-      </c>
-      <c r="D25" s="35" t="n"/>
-      <c r="E25" s="35" t="n"/>
-      <c r="F25" s="35" t="n"/>
+          <t>fsa:ShorttermPayablesToAssociates</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="n">
+        <v>523000</v>
+      </c>
+      <c r="E25" s="35" t="n">
+        <v>645000</v>
+      </c>
+      <c r="F25" s="35" t="n">
+        <v>370000</v>
+      </c>
       <c r="G25" s="35" t="n">
-        <v>149000</v>
+        <v>12000</v>
       </c>
       <c r="H25" s="35" t="n"/>
       <c r="I25" s="36" t="inlineStr">
@@ -8700,12 +8704,12 @@
       </c>
       <c r="B26" s="37" t="inlineStr">
         <is>
-          <t>fsa:SaleOfMinorityShares</t>
+          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
         </is>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
-          <t>fsa:SaleOfMinorityShares</t>
+          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
         </is>
       </c>
       <c r="D26" s="38" t="n"/>
@@ -8713,7 +8717,7 @@
       <c r="F26" s="38" t="n"/>
       <c r="G26" s="38" t="n"/>
       <c r="H26" s="38" t="n">
-        <v>-5000</v>
+        <v>5000</v>
       </c>
       <c r="I26" s="39" t="inlineStr">
         <is>
@@ -8729,27 +8733,25 @@
       </c>
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToAssociates</t>
+          <t>fsa:ShorttermReceivablesFromOwnersAndManagement</t>
         </is>
       </c>
       <c r="C27" s="34" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToAssociates</t>
-        </is>
-      </c>
-      <c r="D27" s="35" t="n">
-        <v>523000</v>
-      </c>
-      <c r="E27" s="35" t="n">
-        <v>645000</v>
-      </c>
+          <t>fsa:ShorttermReceivablesFromOwnersAndManagement</t>
+        </is>
+      </c>
+      <c r="D27" s="35" t="n"/>
+      <c r="E27" s="35" t="n"/>
       <c r="F27" s="35" t="n">
-        <v>370000</v>
+        <v>0</v>
       </c>
       <c r="G27" s="35" t="n">
-        <v>12000</v>
-      </c>
-      <c r="H27" s="35" t="n"/>
+        <v>15000</v>
+      </c>
+      <c r="H27" s="35" t="n">
+        <v>1000</v>
+      </c>
       <c r="I27" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8764,12 +8766,12 @@
       </c>
       <c r="B28" s="37" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
+          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
         </is>
       </c>
       <c r="C28" s="37" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
+          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
         </is>
       </c>
       <c r="D28" s="38" t="n"/>
@@ -8777,7 +8779,7 @@
       <c r="F28" s="38" t="n"/>
       <c r="G28" s="38" t="n"/>
       <c r="H28" s="38" t="n">
-        <v>5000</v>
+        <v>9000</v>
       </c>
       <c r="I28" s="39" t="inlineStr">
         <is>
@@ -8793,84 +8795,22 @@
       </c>
       <c r="B29" s="34" t="inlineStr">
         <is>
-          <t>fsa:ShorttermReceivablesFromOwnersAndManagement</t>
+          <t>fsa:TransferredToFromMinorityInterests</t>
         </is>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>fsa:ShorttermReceivablesFromOwnersAndManagement</t>
+          <t>fsa:TransferredToFromMinorityInterests</t>
         </is>
       </c>
       <c r="D29" s="35" t="n"/>
-      <c r="E29" s="35" t="n"/>
-      <c r="F29" s="35" t="n">
+      <c r="E29" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="35" t="n">
-        <v>15000</v>
-      </c>
-      <c r="H29" s="35" t="n">
-        <v>1000</v>
-      </c>
+      <c r="F29" s="35" t="n"/>
+      <c r="G29" s="35" t="n"/>
+      <c r="H29" s="35" t="n"/>
       <c r="I29" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B30" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="C30" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="D30" s="38" t="n"/>
-      <c r="E30" s="38" t="n"/>
-      <c r="F30" s="38" t="n"/>
-      <c r="G30" s="38" t="n"/>
-      <c r="H30" s="38" t="n">
-        <v>9000</v>
-      </c>
-      <c r="I30" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B31" s="34" t="inlineStr">
-        <is>
-          <t>fsa:TransferredToFromMinorityInterests</t>
-        </is>
-      </c>
-      <c r="C31" s="34" t="inlineStr">
-        <is>
-          <t>fsa:TransferredToFromMinorityInterests</t>
-        </is>
-      </c>
-      <c r="D31" s="35" t="n"/>
-      <c r="E31" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="35" t="n"/>
-      <c r="G31" s="35" t="n"/>
-      <c r="H31" s="35" t="n"/>
-      <c r="I31" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>
